--- a/state/01016_arbigny.xlsx
+++ b/state/01016_arbigny.xlsx
@@ -12381,72 +12381,72 @@
       </c>
       <c r="ID3" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IE3" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IF3" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IG3" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IH3" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="II3" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IJ3" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IK3" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IL3" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IM3" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IN3" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IO3" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IP3" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IQ3" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IR3" t="inlineStr">
@@ -29685,72 +29685,72 @@
       </c>
       <c r="ID10" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IE10" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IF10" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IG10" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IH10" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="II10" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IJ10" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IK10" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IL10" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IM10" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IN10" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IO10" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IP10" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IQ10" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IR10" t="inlineStr">
@@ -32157,72 +32157,72 @@
       </c>
       <c r="ID11" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IE11" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IF11" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IG11" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IH11" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="II11" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IJ11" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IK11" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IL11" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IM11" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IN11" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IO11" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IP11" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IQ11" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IR11" t="inlineStr">
@@ -34629,72 +34629,72 @@
       </c>
       <c r="ID12" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IE12" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IF12" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IG12" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IH12" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="II12" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IJ12" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IK12" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IL12" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IM12" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IN12" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IO12" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IP12" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IQ12" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IR12" t="inlineStr">
@@ -37101,72 +37101,72 @@
       </c>
       <c r="ID13" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IE13" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IF13" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IG13" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IH13" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="II13" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IJ13" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IK13" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IL13" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IM13" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IN13" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IO13" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IP13" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IQ13" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IR13" t="inlineStr">
@@ -39573,72 +39573,72 @@
       </c>
       <c r="ID14" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IE14" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IF14" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IG14" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IH14" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="II14" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IJ14" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IK14" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IL14" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IM14" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IN14" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IO14" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IP14" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IQ14" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IR14" t="inlineStr">
@@ -42045,72 +42045,72 @@
       </c>
       <c r="ID15" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IE15" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IF15" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IG15" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IH15" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="II15" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IJ15" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IK15" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IL15" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IM15" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IN15" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IO15" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IP15" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IQ15" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IR15" t="inlineStr">
@@ -44517,72 +44517,72 @@
       </c>
       <c r="ID16" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IE16" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IF16" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IG16" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IH16" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="II16" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IJ16" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IK16" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IL16" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IM16" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IN16" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IO16" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IP16" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IQ16" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IR16" t="inlineStr">
@@ -46989,72 +46989,72 @@
       </c>
       <c r="ID17" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IE17" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IF17" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IG17" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IH17" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="II17" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IJ17" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IK17" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IL17" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IM17" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IN17" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IO17" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IP17" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IQ17" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IR17" t="inlineStr">
@@ -49461,72 +49461,72 @@
       </c>
       <c r="ID18" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IE18" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IF18" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IG18" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IH18" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="II18" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IJ18" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IK18" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IL18" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IM18" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IN18" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IO18" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IP18" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IQ18" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IR18" t="inlineStr">
@@ -51933,72 +51933,72 @@
       </c>
       <c r="ID19" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IE19" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IF19" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IG19" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IH19" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="II19" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IJ19" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IK19" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IL19" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IM19" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IN19" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IO19" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IP19" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IQ19" t="inlineStr">
         <is>
-          <t>ERREUR</t>
+          <t>N</t>
         </is>
       </c>
       <c r="IR19" t="inlineStr">

--- a/state/01016_arbigny.xlsx
+++ b/state/01016_arbigny.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="21480" yWindow="-165" windowWidth="21840" windowHeight="13140" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Feuil1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feuil1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191028" fullCalcOnLoad="1"/>
@@ -433,7 +433,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -702,6 +702,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -779,7 +782,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
     <from>
       <col>225</col>
@@ -797,24 +800,24 @@
       <nvPicPr>
         <cNvPr id="194" name="Image 193"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId195"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId195"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="175707675" y="95251"/>
           <a:ext cx="228632" cy="228600"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -833,24 +836,24 @@
       <nvPicPr>
         <cNvPr id="2" name="Image 1"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="25195530" y="64770"/>
           <a:ext cx="281964" cy="243861"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -869,24 +872,24 @@
       <nvPicPr>
         <cNvPr id="3" name="Image 2"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="33638490" y="85725"/>
           <a:ext cx="243861" cy="281964"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -905,24 +908,24 @@
       <nvPicPr>
         <cNvPr id="4" name="Image 3"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="72383885" y="123119"/>
           <a:ext cx="404518" cy="258203"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -941,24 +944,24 @@
       <nvPicPr>
         <cNvPr id="5" name="Image 4"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="77679551" y="37982"/>
           <a:ext cx="365792" cy="365792"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -977,24 +980,24 @@
       <nvPicPr>
         <cNvPr id="6" name="Image 5"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="25214580" y="93345"/>
           <a:ext cx="281964" cy="243861"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -1013,24 +1016,24 @@
       <nvPicPr>
         <cNvPr id="7" name="Image 6"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="24385905" y="78105"/>
           <a:ext cx="327688" cy="281964"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -1049,24 +1052,24 @@
       <nvPicPr>
         <cNvPr id="8" name="Image 7"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="25953720" y="121920"/>
           <a:ext cx="281964" cy="243861"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -1085,24 +1088,24 @@
       <nvPicPr>
         <cNvPr id="9" name="Image 8"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId8"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="26567130" y="57150"/>
           <a:ext cx="602032" cy="381033"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -1121,24 +1124,24 @@
       <nvPicPr>
         <cNvPr id="10" name="Image 9"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="27456765" y="81915"/>
           <a:ext cx="312447" cy="281964"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -1157,24 +1160,24 @@
       <nvPicPr>
         <cNvPr id="11" name="Image 10"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId10"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="28186380" y="57150"/>
           <a:ext cx="335309" cy="320068"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -1193,24 +1196,24 @@
       <nvPicPr>
         <cNvPr id="12" name="Image 11"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId11"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="28965525" y="104775"/>
           <a:ext cx="289585" cy="266723"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -1229,24 +1232,24 @@
       <nvPicPr>
         <cNvPr id="13" name="Image 12"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId12"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="29723715" y="66675"/>
           <a:ext cx="320068" cy="281964"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -1265,24 +1268,24 @@
       <nvPicPr>
         <cNvPr id="14" name="Image 13"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId13"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="30466665" y="100965"/>
           <a:ext cx="259102" cy="228620"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -1301,24 +1304,24 @@
       <nvPicPr>
         <cNvPr id="15" name="Image 14"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId14"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="31055310" y="47625"/>
           <a:ext cx="647756" cy="335309"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -1337,24 +1340,24 @@
       <nvPicPr>
         <cNvPr id="16" name="Image 15"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId15"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="32042100" y="83820"/>
           <a:ext cx="297206" cy="320068"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -1373,24 +1376,24 @@
       <nvPicPr>
         <cNvPr id="17" name="Image 16"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId16"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="32596455" y="93345"/>
           <a:ext cx="586791" cy="251482"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -1409,24 +1412,24 @@
       <nvPicPr>
         <cNvPr id="18" name="Image 17"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId17"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="34366200" y="102870"/>
           <a:ext cx="236240" cy="236240"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -1445,24 +1448,24 @@
       <nvPicPr>
         <cNvPr id="19" name="Image 18"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId18"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId18"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="34924365" y="76200"/>
           <a:ext cx="800169" cy="320068"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -1481,24 +1484,24 @@
       <nvPicPr>
         <cNvPr id="20" name="Image 19"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId19"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="36627435" y="123825"/>
           <a:ext cx="274344" cy="228620"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -1517,24 +1520,24 @@
       <nvPicPr>
         <cNvPr id="21" name="Image 20"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId20"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId20"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="37395150" y="95250"/>
           <a:ext cx="266723" cy="281964"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -1553,24 +1556,24 @@
       <nvPicPr>
         <cNvPr id="22" name="Image 21"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId21"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId21"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="38180010" y="133350"/>
           <a:ext cx="220999" cy="236240"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -1589,24 +1592,24 @@
       <nvPicPr>
         <cNvPr id="23" name="Image 22"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId22"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId22"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="38905815" y="133350"/>
           <a:ext cx="220999" cy="175275"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -1625,24 +1628,24 @@
       <nvPicPr>
         <cNvPr id="24" name="Image 23"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId23"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId23"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="39625905" y="114300"/>
           <a:ext cx="342930" cy="243861"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -1661,24 +1664,24 @@
       <nvPicPr>
         <cNvPr id="25" name="Image 24"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId24"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId24"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="40408860" y="123825"/>
           <a:ext cx="274344" cy="228620"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -1697,24 +1700,24 @@
       <nvPicPr>
         <cNvPr id="26" name="Image 25"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId25"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId25"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="40961310" y="57150"/>
           <a:ext cx="861135" cy="335309"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -1733,24 +1736,24 @@
       <nvPicPr>
         <cNvPr id="27" name="Image 26"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId26"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId26"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="41967150" y="114300"/>
           <a:ext cx="228620" cy="251482"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -1769,24 +1772,24 @@
       <nvPicPr>
         <cNvPr id="28" name="Image 27"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId27"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId27"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="42670095" y="123825"/>
           <a:ext cx="320068" cy="236240"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -1805,24 +1808,24 @@
       <nvPicPr>
         <cNvPr id="29" name="Image 28"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId28"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId28"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="43456860" y="100965"/>
           <a:ext cx="281964" cy="297206"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -1841,24 +1844,24 @@
       <nvPicPr>
         <cNvPr id="30" name="Image 29"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId29"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId29"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="44194095" y="123825"/>
           <a:ext cx="312447" cy="243861"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -1877,24 +1880,24 @@
       <nvPicPr>
         <cNvPr id="31" name="Image 30"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId30"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId30"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="44950380" y="66675"/>
           <a:ext cx="312447" cy="281964"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -1913,24 +1916,24 @@
       <nvPicPr>
         <cNvPr id="32" name="Image 31"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId31"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId31"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="45720000" y="95250"/>
           <a:ext cx="274344" cy="297206"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -1949,24 +1952,24 @@
       <nvPicPr>
         <cNvPr id="33" name="Image 32"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId32"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId32"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="46512480" y="133350"/>
           <a:ext cx="274344" cy="251482"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -1985,24 +1988,24 @@
       <nvPicPr>
         <cNvPr id="34" name="Image 33"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId33"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId33"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="48026955" y="146685"/>
           <a:ext cx="289585" cy="243861"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -2021,24 +2024,24 @@
       <nvPicPr>
         <cNvPr id="35" name="Image 34"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId34"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId34"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="47284005" y="139065"/>
           <a:ext cx="259102" cy="251482"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -2057,24 +2060,24 @@
       <nvPicPr>
         <cNvPr id="36" name="Image 35"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId35"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId35"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="49598580" y="66675"/>
           <a:ext cx="220999" cy="281964"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -2093,24 +2096,24 @@
       <nvPicPr>
         <cNvPr id="37" name="Image 36"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId36"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId36"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="48737520" y="66675"/>
           <a:ext cx="342930" cy="327688"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -2129,24 +2132,24 @@
       <nvPicPr>
         <cNvPr id="38" name="Image 37"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId37"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId37"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="50328195" y="95250"/>
           <a:ext cx="335309" cy="243861"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -2165,24 +2168,24 @@
       <nvPicPr>
         <cNvPr id="39" name="Image 38"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId38"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId38"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="51010185" y="144780"/>
           <a:ext cx="449580" cy="259080"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -2201,24 +2204,24 @@
       <nvPicPr>
         <cNvPr id="40" name="Image 39"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId39"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId39"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="52433219" y="41910"/>
           <a:ext cx="693421" cy="335309"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -2237,24 +2240,24 @@
       <nvPicPr>
         <cNvPr id="41" name="Image 40"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId40"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId40"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="53204746" y="123825"/>
           <a:ext cx="693420" cy="259102"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -2273,24 +2276,24 @@
       <nvPicPr>
         <cNvPr id="42" name="Image 41"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId41"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId41"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="54113430" y="83820"/>
           <a:ext cx="411516" cy="335309"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -2309,24 +2312,24 @@
       <nvPicPr>
         <cNvPr id="43" name="Image 42"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId42"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId42"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="54873525" y="76200"/>
           <a:ext cx="365792" cy="274344"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -2345,24 +2348,24 @@
       <nvPicPr>
         <cNvPr id="44" name="Image 43"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId43"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId43"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="55620285" y="43815"/>
           <a:ext cx="441998" cy="312447"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -2381,24 +2384,24 @@
       <nvPicPr>
         <cNvPr id="45" name="Image 44"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId44"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId44"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="56448960" y="118110"/>
           <a:ext cx="236240" cy="251482"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -2417,24 +2420,24 @@
       <nvPicPr>
         <cNvPr id="46" name="Image 45"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId45"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId45"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="57132855" y="64770"/>
           <a:ext cx="381033" cy="281964"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -2453,24 +2456,24 @@
       <nvPicPr>
         <cNvPr id="47" name="Image 46"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId46"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId46"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="57894855" y="99060"/>
           <a:ext cx="419136" cy="281964"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -2489,24 +2492,24 @@
       <nvPicPr>
         <cNvPr id="48" name="Image 47"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId47"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId47"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="58641615" y="142875"/>
           <a:ext cx="464860" cy="236240"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -2525,24 +2528,24 @@
       <nvPicPr>
         <cNvPr id="49" name="Image 48"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId48"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId48"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="59449335" y="68580"/>
           <a:ext cx="358171" cy="289585"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -2561,24 +2564,24 @@
       <nvPicPr>
         <cNvPr id="50" name="Image 49"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId49"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId49"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="60188475" y="80010"/>
           <a:ext cx="396274" cy="259102"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -2597,24 +2600,24 @@
       <nvPicPr>
         <cNvPr id="51" name="Image 50"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId50"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId50"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="60996195" y="142875"/>
           <a:ext cx="281964" cy="220999"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -2633,24 +2636,24 @@
       <nvPicPr>
         <cNvPr id="52" name="Image 51"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId51"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId51"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="61691520" y="76200"/>
           <a:ext cx="449619" cy="304826"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -2669,24 +2672,24 @@
       <nvPicPr>
         <cNvPr id="53" name="Image 52"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId52"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId52"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="62253494" y="47625"/>
           <a:ext cx="693421" cy="373412"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -2705,24 +2708,24 @@
       <nvPicPr>
         <cNvPr id="54" name="Image 53"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId53"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId53"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="63249810" y="93344"/>
           <a:ext cx="373380" cy="282109"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -2741,24 +2744,24 @@
       <nvPicPr>
         <cNvPr id="55" name="Image 54"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId54"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId54"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="64019430" y="120015"/>
           <a:ext cx="335309" cy="198137"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -2777,24 +2780,24 @@
       <nvPicPr>
         <cNvPr id="56" name="Image 55"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId55"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId55"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="64813815" y="76200"/>
           <a:ext cx="312447" cy="297206"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -2813,24 +2816,24 @@
       <nvPicPr>
         <cNvPr id="57" name="Image 56"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId56"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId56"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="65539620" y="129540"/>
           <a:ext cx="304826" cy="213378"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -2849,24 +2852,24 @@
       <nvPicPr>
         <cNvPr id="58" name="Image 57"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId57"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId57"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="66271140" y="76200"/>
           <a:ext cx="449619" cy="342930"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -2885,24 +2888,24 @@
       <nvPicPr>
         <cNvPr id="59" name="Image 58"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId58"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId58"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="67054095" y="62865"/>
           <a:ext cx="327688" cy="304826"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -2921,24 +2924,24 @@
       <nvPicPr>
         <cNvPr id="60" name="Image 59"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId59"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId59"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="67795140" y="85725"/>
           <a:ext cx="335309" cy="251482"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -2957,24 +2960,24 @@
       <nvPicPr>
         <cNvPr id="61" name="Image 60"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId60"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId60"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="68557140" y="99060"/>
           <a:ext cx="342930" cy="274344"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -2993,24 +2996,24 @@
       <nvPicPr>
         <cNvPr id="62" name="Image 61"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId61"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId61"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="69359145" y="34290"/>
           <a:ext cx="297206" cy="297206"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -3029,24 +3032,24 @@
       <nvPicPr>
         <cNvPr id="63" name="Image 62"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId62"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId62"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="69985890" y="68580"/>
           <a:ext cx="723963" cy="304826"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -3065,24 +3068,24 @@
       <nvPicPr>
         <cNvPr id="64" name="Image 63"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId63"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId63"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="73146473" y="66557"/>
           <a:ext cx="289585" cy="304826"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -3101,24 +3104,24 @@
       <nvPicPr>
         <cNvPr id="65" name="Image 64"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId64"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId64"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="73888012" y="85372"/>
           <a:ext cx="327688" cy="251482"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -3137,24 +3140,24 @@
       <nvPicPr>
         <cNvPr id="66" name="Image 65"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId65"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId65"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="75415893" y="141818"/>
           <a:ext cx="297206" cy="251482"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -3173,24 +3176,24 @@
       <nvPicPr>
         <cNvPr id="67" name="Image 66"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId66"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId66"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="76203528" y="132409"/>
           <a:ext cx="281964" cy="220999"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -3209,24 +3212,24 @@
       <nvPicPr>
         <cNvPr id="68" name="Image 67"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId67"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId67"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="78479415" y="84667"/>
           <a:ext cx="419136" cy="327688"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -3245,24 +3248,24 @@
       <nvPicPr>
         <cNvPr id="69" name="Image 68"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId68"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId68"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="79113592" y="66558"/>
           <a:ext cx="838273" cy="327688"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -3281,24 +3284,24 @@
       <nvPicPr>
         <cNvPr id="70" name="Image 69"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId69"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId69"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="80025875" y="103835"/>
           <a:ext cx="320068" cy="266723"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -3317,24 +3320,24 @@
       <nvPicPr>
         <cNvPr id="71" name="Image 70"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId70"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId70"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="80795871" y="113359"/>
           <a:ext cx="358171" cy="266723"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -3353,24 +3356,24 @@
       <nvPicPr>
         <cNvPr id="72" name="Image 71"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId71"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId71"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="81519066" y="56799"/>
           <a:ext cx="381033" cy="274344"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -3389,24 +3392,24 @@
       <nvPicPr>
         <cNvPr id="73" name="Image 72"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId72"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId72"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="82317285" y="75730"/>
           <a:ext cx="365792" cy="289585"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -3425,24 +3428,24 @@
       <nvPicPr>
         <cNvPr id="74" name="Image 73"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId73"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId73"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="83040008" y="75377"/>
           <a:ext cx="297206" cy="236240"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -3461,24 +3464,24 @@
       <nvPicPr>
         <cNvPr id="75" name="Image 74"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId74"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId74"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="83769788" y="94309"/>
           <a:ext cx="327688" cy="297206"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -3497,24 +3500,24 @@
       <nvPicPr>
         <cNvPr id="76" name="Image 75"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId75"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId75"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="84606224" y="103482"/>
           <a:ext cx="297206" cy="228620"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -3533,24 +3536,24 @@
       <nvPicPr>
         <cNvPr id="77" name="Image 76"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId76"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId76"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="85306253" y="66322"/>
           <a:ext cx="335309" cy="350550"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -3569,24 +3572,24 @@
       <nvPicPr>
         <cNvPr id="78" name="Image 77"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId77"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId77"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="86159622" y="75495"/>
           <a:ext cx="274344" cy="274344"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -3605,24 +3608,24 @@
       <nvPicPr>
         <cNvPr id="79" name="Image 78"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId78"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId78"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="87633731" y="100406"/>
           <a:ext cx="352474" cy="257211"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -3641,24 +3644,24 @@
       <nvPicPr>
         <cNvPr id="80" name="Image 79"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId79"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId79"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="88250653" y="68321"/>
           <a:ext cx="571580" cy="323895"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -3677,24 +3680,24 @@
       <nvPicPr>
         <cNvPr id="81" name="Image 80"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId80"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId80"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="88979139" y="83962"/>
           <a:ext cx="647790" cy="295316"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -3713,24 +3716,24 @@
       <nvPicPr>
         <cNvPr id="82" name="Image 81"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId81"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId81"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="89751253" y="105245"/>
           <a:ext cx="571580" cy="247685"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -3749,24 +3752,24 @@
       <nvPicPr>
         <cNvPr id="83" name="Image 82"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId82"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId82"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="90578634" y="76671"/>
           <a:ext cx="562053" cy="333422"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -3785,24 +3788,24 @@
       <nvPicPr>
         <cNvPr id="84" name="Image 83"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId83"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId83"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="91458345" y="112536"/>
           <a:ext cx="285790" cy="266737"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -3821,24 +3824,24 @@
       <nvPicPr>
         <cNvPr id="85" name="Image 84"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId84"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId84"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="92199060" y="112536"/>
           <a:ext cx="314369" cy="199908"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -3857,24 +3860,24 @@
       <nvPicPr>
         <cNvPr id="86" name="Image 85"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId85"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId85"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="93001393" y="91251"/>
           <a:ext cx="304843" cy="238158"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -3893,24 +3896,24 @@
       <nvPicPr>
         <cNvPr id="87" name="Image 86"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId86"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId86"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="93720826" y="74436"/>
           <a:ext cx="342948" cy="285790"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -3929,24 +3932,24 @@
       <nvPicPr>
         <cNvPr id="88" name="Image 87"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId87"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId87"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="95263876" y="84549"/>
           <a:ext cx="276264" cy="276264"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -3965,24 +3968,24 @@
       <nvPicPr>
         <cNvPr id="89" name="Image 88"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId88"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId88"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="94446960" y="46449"/>
           <a:ext cx="428685" cy="323895"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -4001,24 +4004,24 @@
       <nvPicPr>
         <cNvPr id="90" name="Image 89"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId89"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId89"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="96015763" y="118180"/>
           <a:ext cx="238158" cy="219106"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -4037,24 +4040,24 @@
       <nvPicPr>
         <cNvPr id="91" name="Image 90"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId90"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId90"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="96796813" y="96308"/>
           <a:ext cx="285790" cy="247685"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -4073,24 +4076,24 @@
       <nvPicPr>
         <cNvPr id="92" name="Image 91"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId91"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId91"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="97528004" y="96308"/>
           <a:ext cx="238158" cy="266737"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -4109,24 +4112,24 @@
       <nvPicPr>
         <cNvPr id="93" name="Image 92"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId92"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId92"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="98320696" y="99131"/>
           <a:ext cx="285790" cy="247685"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -4145,24 +4148,24 @@
       <nvPicPr>
         <cNvPr id="94" name="Image 93"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId93"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId93"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="99057649" y="98543"/>
           <a:ext cx="323895" cy="266737"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -4181,24 +4184,24 @@
       <nvPicPr>
         <cNvPr id="95" name="Image 94"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId94"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId94"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="99672033" y="89246"/>
           <a:ext cx="611481" cy="333422"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -4217,24 +4220,24 @@
       <nvPicPr>
         <cNvPr id="96" name="Image 95"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId95"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId95"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="100637622" y="119239"/>
           <a:ext cx="200053" cy="219106"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -4253,24 +4256,24 @@
       <nvPicPr>
         <cNvPr id="97" name="Image 96"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId96"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId96"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="101270859" y="69968"/>
           <a:ext cx="552686" cy="295316"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -4289,24 +4292,24 @@
       <nvPicPr>
         <cNvPr id="98" name="Image 97"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId97"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId97"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="102103884" y="75023"/>
           <a:ext cx="314369" cy="266737"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -4325,24 +4328,24 @@
       <nvPicPr>
         <cNvPr id="99" name="Image 98"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId98"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId98"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="102833429" y="35694"/>
           <a:ext cx="364536" cy="286421"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -4361,24 +4364,24 @@
       <nvPicPr>
         <cNvPr id="100" name="Image 99"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId99"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId99"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="103681154" y="89606"/>
           <a:ext cx="323895" cy="304843"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -4397,24 +4400,24 @@
       <nvPicPr>
         <cNvPr id="101" name="Image 100"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId100"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId100"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="104398350" y="79493"/>
           <a:ext cx="333422" cy="266737"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -4433,24 +4436,24 @@
       <nvPicPr>
         <cNvPr id="102" name="Image 101"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId101"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId101"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="105037702" y="75612"/>
           <a:ext cx="540926" cy="314369"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -4469,24 +4472,24 @@
       <nvPicPr>
         <cNvPr id="103" name="Image 102"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId102"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId102"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="105910592" y="117591"/>
           <a:ext cx="352474" cy="238158"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -4505,24 +4508,24 @@
       <nvPicPr>
         <cNvPr id="104" name="Image 103"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId103"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId103"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="106658009" y="113124"/>
           <a:ext cx="409632" cy="238158"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -4541,24 +4544,24 @@
       <nvPicPr>
         <cNvPr id="105" name="Image 104"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId104"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId104"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="107414131" y="89606"/>
           <a:ext cx="304843" cy="257211"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -4577,24 +4580,24 @@
       <nvPicPr>
         <cNvPr id="106" name="Image 105"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId105"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId105"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="109400035" y="99131"/>
           <a:ext cx="333422" cy="276264"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -4613,24 +4616,24 @@
       <nvPicPr>
         <cNvPr id="107" name="Image 106"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId106"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId106"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="110170970" y="77847"/>
           <a:ext cx="333422" cy="285790"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -4649,24 +4652,24 @@
       <nvPicPr>
         <cNvPr id="108" name="Image 107"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId107"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId107"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="110931208" y="118179"/>
           <a:ext cx="304843" cy="266737"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -4685,24 +4688,24 @@
       <nvPicPr>
         <cNvPr id="109" name="Image 108"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId108"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId108"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="111556212" y="157339"/>
           <a:ext cx="613508" cy="199908"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -4721,24 +4724,24 @@
       <nvPicPr>
         <cNvPr id="110" name="Image 109"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId109"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId109"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="112468260" y="91252"/>
           <a:ext cx="352474" cy="285790"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -4757,24 +4760,24 @@
       <nvPicPr>
         <cNvPr id="111" name="Image 110"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId110"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId110"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="113240374" y="127118"/>
           <a:ext cx="352474" cy="285790"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -4793,24 +4796,24 @@
       <nvPicPr>
         <cNvPr id="112" name="Image 111"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId111"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId111"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="113987792" y="103011"/>
           <a:ext cx="352474" cy="285790"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -4829,24 +4832,24 @@
       <nvPicPr>
         <cNvPr id="113" name="Image 112"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId112"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId112"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="114590218" y="91252"/>
           <a:ext cx="493889" cy="314369"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -4865,24 +4868,24 @@
       <nvPicPr>
         <cNvPr id="114" name="Image 113"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId113"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId113"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="115539191" y="91839"/>
           <a:ext cx="371527" cy="257211"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -4901,24 +4904,24 @@
       <nvPicPr>
         <cNvPr id="115" name="Image 114"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId114"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId114"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="116321887" y="113124"/>
           <a:ext cx="314369" cy="276264"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -4937,24 +4940,24 @@
       <nvPicPr>
         <cNvPr id="116" name="Image 115"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId115"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId115"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="117014978" y="129939"/>
           <a:ext cx="362001" cy="219106"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -4973,24 +4976,24 @@
       <nvPicPr>
         <cNvPr id="117" name="Image 116"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId116"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId116"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="117803906" y="96309"/>
           <a:ext cx="352474" cy="257211"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -5009,24 +5012,24 @@
       <nvPicPr>
         <cNvPr id="118" name="Image 117"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId117"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId117"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="118542547" y="96931"/>
           <a:ext cx="371527" cy="285790"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -5045,24 +5048,24 @@
       <nvPicPr>
         <cNvPr id="119" name="Image 118"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId118"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId118"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="119371222" y="62193"/>
           <a:ext cx="266737" cy="304843"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -5081,24 +5084,24 @@
       <nvPicPr>
         <cNvPr id="120" name="Image 119"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId119"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId119"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="120080555" y="137273"/>
           <a:ext cx="285790" cy="219106"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -5117,24 +5120,24 @@
       <nvPicPr>
         <cNvPr id="121" name="Image 120"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId120"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId120"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="120857577" y="93149"/>
           <a:ext cx="304843" cy="285790"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -5153,24 +5156,24 @@
       <nvPicPr>
         <cNvPr id="122" name="Image 121"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId121"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId121"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="123169349" y="115736"/>
           <a:ext cx="314369" cy="257211"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -5189,24 +5192,24 @@
       <nvPicPr>
         <cNvPr id="123" name="Image 122"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId122"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId122"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="123740326" y="110693"/>
           <a:ext cx="628738" cy="238158"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -5225,24 +5228,24 @@
       <nvPicPr>
         <cNvPr id="124" name="Image 123"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId123"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId123"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="124632136" y="109013"/>
           <a:ext cx="342948" cy="228632"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -5261,24 +5264,24 @@
       <nvPicPr>
         <cNvPr id="125" name="Image 124"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId124"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId124"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="126192068" y="113285"/>
           <a:ext cx="285790" cy="219106"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -5297,24 +5300,24 @@
       <nvPicPr>
         <cNvPr id="126" name="Image 125"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId125"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId125"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="126854931" y="130655"/>
           <a:ext cx="438211" cy="247685"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -5333,24 +5336,24 @@
       <nvPicPr>
         <cNvPr id="127" name="Image 126"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId126"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId126"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="127661088" y="124174"/>
           <a:ext cx="371527" cy="209579"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -5369,24 +5372,24 @@
       <nvPicPr>
         <cNvPr id="128" name="Image 127"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId127"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId127"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="129033074" y="152155"/>
           <a:ext cx="685993" cy="224117"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -5405,24 +5408,24 @@
       <nvPicPr>
         <cNvPr id="129" name="Image 128"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId128"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId128"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="128469067" y="134996"/>
           <a:ext cx="352474" cy="257211"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -5441,24 +5444,24 @@
       <nvPicPr>
         <cNvPr id="130" name="Image 129"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId129"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId129"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="131483101" y="116543"/>
           <a:ext cx="371527" cy="219106"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -5477,24 +5480,24 @@
       <nvPicPr>
         <cNvPr id="131" name="Image 130"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId130"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId130"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="132250703" y="99173"/>
           <a:ext cx="390580" cy="285790"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -5513,24 +5516,24 @@
       <nvPicPr>
         <cNvPr id="132" name="Image 131"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId131"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId131"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="133851780" y="129288"/>
           <a:ext cx="304843" cy="238158"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -5549,24 +5552,24 @@
       <nvPicPr>
         <cNvPr id="133" name="Image 132"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId132"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId132"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="130782172" y="111499"/>
           <a:ext cx="352474" cy="257211"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -5585,24 +5588,24 @@
       <nvPicPr>
         <cNvPr id="134" name="Image 133"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId133"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId133"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="130054911" y="126067"/>
           <a:ext cx="314369" cy="257735"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -5621,24 +5624,24 @@
       <nvPicPr>
         <cNvPr id="135" name="Image 134"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId134"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId134"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="133018867" y="121025"/>
           <a:ext cx="371527" cy="219106"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -5657,24 +5660,24 @@
       <nvPicPr>
         <cNvPr id="136" name="Image 135"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId135"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId135"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="134530609" y="130794"/>
           <a:ext cx="304843" cy="219106"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -5693,24 +5696,24 @@
       <nvPicPr>
         <cNvPr id="137" name="Image 136"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId136"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId136"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="135297127" y="74279"/>
           <a:ext cx="504264" cy="275053"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -5729,24 +5732,24 @@
       <nvPicPr>
         <cNvPr id="138" name="Image 137"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId137"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId137"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="136057901" y="128308"/>
           <a:ext cx="409632" cy="209579"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -5765,24 +5768,24 @@
       <nvPicPr>
         <cNvPr id="139" name="Image 138"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId138"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId138"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="136821583" y="85164"/>
           <a:ext cx="390580" cy="266737"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -5801,24 +5804,24 @@
       <nvPicPr>
         <cNvPr id="140" name="Image 139"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId139"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId139"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="137609356" y="107577"/>
           <a:ext cx="428685" cy="238158"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -5837,24 +5840,24 @@
       <nvPicPr>
         <cNvPr id="141" name="Image 140"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId140"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId140"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="138314627" y="104494"/>
           <a:ext cx="438211" cy="295316"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -5873,24 +5876,24 @@
       <nvPicPr>
         <cNvPr id="142" name="Image 141"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId141"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId141"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="139140079" y="117102"/>
           <a:ext cx="352474" cy="266737"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -5909,24 +5912,24 @@
       <nvPicPr>
         <cNvPr id="143" name="Image 142"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId142"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId142"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="139909924" y="139513"/>
           <a:ext cx="352474" cy="276264"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -5945,24 +5948,24 @@
       <nvPicPr>
         <cNvPr id="144" name="Image 143"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId143"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId143"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="140625419" y="107576"/>
           <a:ext cx="362001" cy="238158"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -5981,24 +5984,24 @@
       <nvPicPr>
         <cNvPr id="145" name="Image 144"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId144"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId144"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="141427760" y="91328"/>
           <a:ext cx="342948" cy="276264"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -6017,24 +6020,24 @@
       <nvPicPr>
         <cNvPr id="146" name="Image 145"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId145"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId145"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="142167348" y="131670"/>
           <a:ext cx="352474" cy="276264"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -6053,24 +6056,24 @@
       <nvPicPr>
         <cNvPr id="147" name="Image 146"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId146"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId146"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="142916462" y="107577"/>
           <a:ext cx="371527" cy="285790"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -6089,24 +6092,24 @@
       <nvPicPr>
         <cNvPr id="148" name="Image 147"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId147"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId147"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="143684625" y="104214"/>
           <a:ext cx="371527" cy="295316"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -6125,24 +6128,24 @@
       <nvPicPr>
         <cNvPr id="149" name="Image 148"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId148"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId148"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="144478561" y="156882"/>
           <a:ext cx="314369" cy="209579"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -6161,24 +6164,24 @@
       <nvPicPr>
         <cNvPr id="150" name="Image 149"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId149"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId149"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="145221512" y="153521"/>
           <a:ext cx="333422" cy="247685"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -6197,24 +6200,24 @@
       <nvPicPr>
         <cNvPr id="151" name="Image 150"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId150"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId150"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="145945412" y="100853"/>
           <a:ext cx="390580" cy="266737"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -6233,24 +6236,24 @@
       <nvPicPr>
         <cNvPr id="152" name="Image 151"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId151"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId151"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="146718617" y="100853"/>
           <a:ext cx="314369" cy="219106"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -6269,24 +6272,24 @@
       <nvPicPr>
         <cNvPr id="153" name="Image 152"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId152"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId152"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="147504710" y="121584"/>
           <a:ext cx="314369" cy="238158"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -6305,24 +6308,24 @@
       <nvPicPr>
         <cNvPr id="154" name="Image 153"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId153"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId153"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="148258306" y="100853"/>
           <a:ext cx="409632" cy="219106"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -6341,24 +6344,24 @@
       <nvPicPr>
         <cNvPr id="155" name="Image 154"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId154"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId154"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="149061767" y="118222"/>
           <a:ext cx="276264" cy="257211"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -6377,24 +6380,24 @@
       <nvPicPr>
         <cNvPr id="156" name="Image 155"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId155"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId155"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="149822087" y="142315"/>
           <a:ext cx="314369" cy="219106"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -6413,24 +6416,24 @@
       <nvPicPr>
         <cNvPr id="157" name="Image 156"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId156"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId156"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="150584086" y="107016"/>
           <a:ext cx="352474" cy="276264"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -6449,24 +6452,24 @@
       <nvPicPr>
         <cNvPr id="158" name="Image 157"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId157"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId157"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="151319193" y="116542"/>
           <a:ext cx="304843" cy="257211"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -6485,24 +6488,24 @@
       <nvPicPr>
         <cNvPr id="159" name="Image 158"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId158"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId158"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="152127137" y="134470"/>
           <a:ext cx="314369" cy="219106"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -6521,24 +6524,24 @@
       <nvPicPr>
         <cNvPr id="160" name="Image 159"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId159"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId159"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="152842632" y="121584"/>
           <a:ext cx="342948" cy="238158"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -6557,24 +6560,24 @@
       <nvPicPr>
         <cNvPr id="161" name="Image 160"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId160"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId160"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="153660661" y="123265"/>
           <a:ext cx="333422" cy="247685"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -6593,24 +6596,24 @@
       <nvPicPr>
         <cNvPr id="162" name="Image 161"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId161"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId161"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="154385122" y="144557"/>
           <a:ext cx="381053" cy="219106"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -6629,24 +6632,24 @@
       <nvPicPr>
         <cNvPr id="163" name="Image 162"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId162"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId162"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="155162250" y="142315"/>
           <a:ext cx="314369" cy="247685"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -6665,24 +6668,24 @@
       <nvPicPr>
         <cNvPr id="164" name="Image 163"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId163"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId163"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="155912484" y="143996"/>
           <a:ext cx="314369" cy="247685"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -6701,24 +6704,24 @@
       <nvPicPr>
         <cNvPr id="165" name="Image 164"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId164"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId164"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="156662717" y="129429"/>
           <a:ext cx="314369" cy="247685"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -6737,24 +6740,24 @@
       <nvPicPr>
         <cNvPr id="166" name="Image 165"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId165"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId165"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="158172702" y="138953"/>
           <a:ext cx="347431" cy="224118"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -6773,24 +6776,24 @@
       <nvPicPr>
         <cNvPr id="167" name="Image 166"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId166"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId166"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="158972250" y="99172"/>
           <a:ext cx="295316" cy="257211"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -6809,24 +6812,24 @@
       <nvPicPr>
         <cNvPr id="168" name="Image 167"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId167"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId167"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="159707356" y="81803"/>
           <a:ext cx="342948" cy="276264"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -6845,24 +6848,24 @@
       <nvPicPr>
         <cNvPr id="169" name="Image 168"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId168"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId168"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="160481122" y="94130"/>
           <a:ext cx="304843" cy="257211"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -6881,24 +6884,24 @@
       <nvPicPr>
         <cNvPr id="170" name="Image 169"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId169"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId169"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="161249285" y="119903"/>
           <a:ext cx="342948" cy="238158"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -6917,24 +6920,24 @@
       <nvPicPr>
         <cNvPr id="171" name="Image 170"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId170"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId170"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="161959178" y="154641"/>
           <a:ext cx="285790" cy="200053"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -6953,24 +6956,24 @@
       <nvPicPr>
         <cNvPr id="172" name="Image 171"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId171"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId171"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="162712213" y="121024"/>
           <a:ext cx="352474" cy="228632"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -6989,24 +6992,24 @@
       <nvPicPr>
         <cNvPr id="173" name="Image 172"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId172"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId172"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="164293924" y="105335"/>
           <a:ext cx="304843" cy="228632"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -7025,24 +7028,24 @@
       <nvPicPr>
         <cNvPr id="174" name="Image 173"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId173"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId173"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="163496063" y="57150"/>
           <a:ext cx="314369" cy="333422"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -7061,24 +7064,24 @@
       <nvPicPr>
         <cNvPr id="175" name="Image 174"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId174"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId174"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="165057603" y="60512"/>
           <a:ext cx="314369" cy="333422"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -7097,24 +7100,24 @@
       <nvPicPr>
         <cNvPr id="176" name="Image 175"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId175"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId175"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="165731638" y="62193"/>
           <a:ext cx="342948" cy="276264"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -7133,24 +7136,24 @@
       <nvPicPr>
         <cNvPr id="177" name="Image 176"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId176"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId176"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="166592810" y="105335"/>
           <a:ext cx="276264" cy="247685"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -7169,24 +7172,24 @@
       <nvPicPr>
         <cNvPr id="178" name="Image 177"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId177"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId177"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="167317831" y="137272"/>
           <a:ext cx="304843" cy="266737"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -7205,24 +7208,24 @@
       <nvPicPr>
         <cNvPr id="179" name="Image 178"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId178"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId178"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="168047894" y="99172"/>
           <a:ext cx="333422" cy="238158"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -7241,24 +7244,24 @@
       <nvPicPr>
         <cNvPr id="180" name="Image 179"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId179"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId179"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="169635768" y="97492"/>
           <a:ext cx="333422" cy="285790"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -7277,24 +7280,24 @@
       <nvPicPr>
         <cNvPr id="181" name="Image 180"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId180"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId180"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="168907385" y="70597"/>
           <a:ext cx="276264" cy="276264"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -7313,24 +7316,24 @@
       <nvPicPr>
         <cNvPr id="182" name="Image 181"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId181"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId181"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="170382079" y="119903"/>
           <a:ext cx="295316" cy="219106"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -7349,24 +7352,24 @@
       <nvPicPr>
         <cNvPr id="183" name="Image 182"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId182"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId182"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="171128391" y="100853"/>
           <a:ext cx="295316" cy="219106"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -7385,24 +7388,24 @@
       <nvPicPr>
         <cNvPr id="184" name="Image 183"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId183"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId183"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="171926250" y="131109"/>
           <a:ext cx="295316" cy="219106"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -7421,24 +7424,24 @@
       <nvPicPr>
         <cNvPr id="185" name="Image 184"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId184"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId184"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="172701137" y="54348"/>
           <a:ext cx="295316" cy="276264"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -7457,24 +7460,24 @@
       <nvPicPr>
         <cNvPr id="186" name="Image 185"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId185"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId185"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="173404306" y="67235"/>
           <a:ext cx="381053" cy="333422"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -7493,24 +7496,24 @@
       <nvPicPr>
         <cNvPr id="187" name="Image 186"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId186"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId186"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="174199923" y="93009"/>
           <a:ext cx="323895" cy="247685"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -7529,24 +7532,24 @@
       <nvPicPr>
         <cNvPr id="188" name="Image 187"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId187"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId187"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="174956880" y="94690"/>
           <a:ext cx="342948" cy="266737"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -7565,24 +7568,24 @@
       <nvPicPr>
         <cNvPr id="189" name="Image 188"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId188"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId188"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="177229853" y="81103"/>
           <a:ext cx="352474" cy="266737"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -7601,24 +7604,24 @@
       <nvPicPr>
         <cNvPr id="190" name="Image 189"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId189"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId189"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="176465193" y="95810"/>
           <a:ext cx="304843" cy="228632"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -7637,24 +7640,24 @@
       <nvPicPr>
         <cNvPr id="191" name="Image 190"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId190"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId190"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="125401876" y="100678"/>
           <a:ext cx="342948" cy="228632"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -7673,24 +7676,24 @@
       <nvPicPr>
         <cNvPr id="192" name="Image 191"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId191"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId191"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="122368060" y="113390"/>
           <a:ext cx="285790" cy="224118"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -7709,24 +7712,24 @@
       <nvPicPr>
         <cNvPr id="193" name="Image 192"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId192"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId192"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="121635055" y="106842"/>
           <a:ext cx="304843" cy="285790"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -7745,24 +7748,24 @@
       <nvPicPr>
         <cNvPr id="195" name="Image 194"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId193"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId193"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="23469600" y="200025"/>
           <a:ext cx="573211" cy="289560"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -7781,24 +7784,24 @@
       <nvPicPr>
         <cNvPr id="196" name="Image 195"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId194"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId194"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="157424717" y="129429"/>
           <a:ext cx="314369" cy="247685"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -8362,7 +8365,11 @@
       <c r="HJ1" s="84" t="n"/>
       <c r="HK1" s="84" t="n"/>
       <c r="HL1" s="84" t="n"/>
-      <c r="HM1" s="84" t="n"/>
+      <c r="HM1" s="92" t="inlineStr">
+        <is>
+          <t>GEORISQUE</t>
+        </is>
+      </c>
       <c r="HN1" s="84" t="n"/>
       <c r="HO1" s="84" t="n"/>
       <c r="HP1" s="84" t="n"/>
@@ -8533,48 +8540,62 @@
       <c r="MJ1" s="5" t="n"/>
       <c r="MK1" s="5" t="n"/>
       <c r="ML1" s="5" t="n"/>
-      <c r="MM1" s="5" t="n"/>
-      <c r="MN1" s="5" t="n"/>
-      <c r="MO1" s="5" t="n"/>
-      <c r="MP1" s="5" t="n"/>
-      <c r="MQ1" s="5" t="n"/>
-      <c r="MR1" s="5" t="n"/>
-      <c r="MS1" s="5" t="n"/>
-      <c r="MT1" s="5" t="n"/>
-      <c r="MU1" s="5" t="n"/>
-      <c r="MV1" s="5" t="n"/>
-      <c r="MW1" s="5" t="n"/>
-      <c r="MX1" s="5" t="n"/>
-      <c r="MY1" s="5" t="n"/>
-      <c r="MZ1" s="5" t="n"/>
-      <c r="NA1" s="5" t="n"/>
-      <c r="NB1" s="5" t="n"/>
-      <c r="NC1" s="5" t="n"/>
-      <c r="ND1" s="5" t="n"/>
-      <c r="NE1" s="5" t="n"/>
-      <c r="NF1" s="5" t="n"/>
-      <c r="NG1" s="5" t="n"/>
-      <c r="NH1" s="5" t="n"/>
-      <c r="NI1" s="5" t="n"/>
-      <c r="NJ1" s="5" t="n"/>
-      <c r="NK1" s="5" t="n"/>
-      <c r="NL1" s="5" t="n"/>
-      <c r="NM1" s="5" t="n"/>
-      <c r="NN1" s="5" t="n"/>
-      <c r="NO1" s="5" t="n"/>
-      <c r="NP1" s="5" t="n"/>
+      <c r="MM1" s="87" t="inlineStr">
+        <is>
+          <t>Plans de prévention des risques
+(PPR-Commune)</t>
+        </is>
+      </c>
+      <c r="MN1" s="91" t="n"/>
+      <c r="MO1" s="91" t="n"/>
+      <c r="MP1" s="91" t="n"/>
+      <c r="MQ1" s="91" t="n"/>
+      <c r="MR1" s="91" t="n"/>
+      <c r="MS1" s="91" t="n"/>
+      <c r="MT1" s="91" t="n"/>
+      <c r="MU1" s="91" t="n"/>
+      <c r="MV1" s="91" t="n"/>
+      <c r="MW1" s="91" t="n"/>
+      <c r="MX1" s="91" t="n"/>
+      <c r="MY1" s="91" t="n"/>
+      <c r="MZ1" s="91" t="n"/>
+      <c r="NA1" s="91" t="n"/>
+      <c r="NB1" s="91" t="n"/>
+      <c r="NC1" s="91" t="n"/>
+      <c r="ND1" s="91" t="n"/>
+      <c r="NE1" s="91" t="n"/>
+      <c r="NF1" s="91" t="n"/>
+      <c r="NG1" s="91" t="n"/>
+      <c r="NH1" s="90" t="n"/>
+      <c r="NI1" s="88" t="inlineStr">
+        <is>
+          <t>Plans de prévention des risques
+(Servitudes d'utilité publique SUP)</t>
+        </is>
+      </c>
+      <c r="NJ1" s="91" t="n"/>
+      <c r="NK1" s="91" t="n"/>
+      <c r="NL1" s="91" t="n"/>
+      <c r="NM1" s="91" t="n"/>
+      <c r="NN1" s="91" t="n"/>
+      <c r="NO1" s="91" t="n"/>
+      <c r="NP1" s="90" t="n"/>
       <c r="NQ1" s="5" t="n"/>
       <c r="NR1" s="5" t="n"/>
       <c r="NS1" s="5" t="n"/>
       <c r="NT1" s="5" t="n"/>
       <c r="NU1" s="5" t="n"/>
       <c r="NV1" s="5" t="n"/>
-      <c r="NW1" s="5" t="n"/>
-      <c r="NX1" s="5" t="n"/>
-      <c r="NY1" s="5" t="n"/>
-      <c r="NZ1" s="5" t="n"/>
-      <c r="OA1" s="5" t="n"/>
-      <c r="OB1" s="5" t="n"/>
+      <c r="NW1" s="81" t="inlineStr">
+        <is>
+          <t>Sites et sols (Potentiellement) pollués</t>
+        </is>
+      </c>
+      <c r="NX1" s="91" t="n"/>
+      <c r="NY1" s="91" t="n"/>
+      <c r="NZ1" s="91" t="n"/>
+      <c r="OA1" s="91" t="n"/>
+      <c r="OB1" s="90" t="n"/>
       <c r="OC1" s="5" t="n"/>
       <c r="OD1" s="5" t="n"/>
       <c r="OE1" s="5" t="n"/>
@@ -53218,14 +53239,17 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="11">
+    <mergeCell ref="NW1:OB1"/>
     <mergeCell ref="HX1:HZ1"/>
     <mergeCell ref="KE1:KI1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="JW1:JY1"/>
+    <mergeCell ref="MM1:NH1"/>
     <mergeCell ref="JO1:JV1"/>
     <mergeCell ref="IV1:JC1"/>
     <mergeCell ref="KA1:KD1"/>
+    <mergeCell ref="NI1:NP1"/>
     <mergeCell ref="JD1:JN1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
